--- a/data_raw/SOFR_latest.xlsx
+++ b/data_raw/SOFR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C443"/>
+  <dimension ref="A1:C444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6191,6 +6191,19 @@
         <v>2963</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="C444" t="n">
+        <v>2961</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/SOFR_latest.xlsx
+++ b/data_raw/SOFR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C444"/>
+  <dimension ref="A1:C447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6204,6 +6204,45 @@
         <v>2961</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="C445" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="C446" t="n">
+        <v>2974</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="C447" t="n">
+        <v>3025</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/SOFR_latest.xlsx
+++ b/data_raw/SOFR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C447"/>
+  <dimension ref="A1:C449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6243,6 +6243,32 @@
         <v>3025</v>
       </c>
     </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="C448" t="n">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="C449" t="n">
+        <v>2888</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/SOFR_latest.xlsx
+++ b/data_raw/SOFR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C449"/>
+  <dimension ref="A1:C452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6269,6 +6269,45 @@
         <v>2888</v>
       </c>
     </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="C450" t="n">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="C451" t="n">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="C452" t="n">
+        <v>2945</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/SOFR_latest.xlsx
+++ b/data_raw/SOFR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C452"/>
+  <dimension ref="A1:C454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6308,6 +6308,32 @@
         <v>2945</v>
       </c>
     </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="C453" t="n">
+        <v>3065</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>0.0393</v>
+      </c>
+      <c r="C454" t="n">
+        <v>3086</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/SOFR_latest.xlsx
+++ b/data_raw/SOFR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C454"/>
+  <dimension ref="A1:C457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6334,6 +6334,45 @@
         <v>3086</v>
       </c>
     </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>0.0395</v>
+      </c>
+      <c r="C455" t="n">
+        <v>3147</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>0.0394</v>
+      </c>
+      <c r="C456" t="n">
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>0.0394</v>
+      </c>
+      <c r="C457" t="n">
+        <v>3145</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
